--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_24_R3.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_24_R3.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.4698</v>
+        <v>7.4613</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8943</v>
+        <v>5.7514</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5755</v>
+        <v>1.71</v>
       </c>
       <c r="G2" t="n">
         <v>2.2948</v>
@@ -610,13 +610,13 @@
         <v>3.7112</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8224</v>
+        <v>0.1691</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4165</v>
+        <v>0.4406</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4059</v>
+        <v>-0.2715</v>
       </c>
       <c r="V2" t="n">
         <v>1.7501</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0151</v>
+        <v>4.2618</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7802</v>
+        <v>2.9598</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2349</v>
+        <v>1.3021</v>
       </c>
       <c r="G3" t="n">
         <v>1.3567</v>
@@ -688,13 +688,13 @@
         <v>3.2473</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6431</v>
+        <v>0.6036</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3497</v>
+        <v>0.8298</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2934</v>
+        <v>-0.2262</v>
       </c>
       <c r="V3" t="n">
         <v>0.6778999999999999</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8506</v>
+        <v>3.0199</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3249</v>
+        <v>0.1469</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1755</v>
+        <v>2.873</v>
       </c>
       <c r="G4" t="n">
         <v>1.3801</v>
@@ -766,13 +766,13 @@
         <v>2.3195</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0066</v>
+        <v>0.1759</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4991</v>
+        <v>-0.0272</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5056</v>
+        <v>0.2032</v>
       </c>
       <c r="V4" t="n">
         <v>0.5361</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0427</v>
+        <v>2.8325</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3507</v>
+        <v>0.5064</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3933</v>
+        <v>2.3261</v>
       </c>
       <c r="G5" t="n">
         <v>1.2343</v>
@@ -844,13 +844,13 @@
         <v>3.7112</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5834</v>
+        <v>0.2065</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5737</v>
+        <v>0.2833</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0097</v>
+        <v>-0.0769</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7727</v>
+        <v>1.2001</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9213</v>
+        <v>1.4495</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1486</v>
+        <v>-0.2494</v>
       </c>
       <c r="G6" t="n">
         <v>2.1955</v>
@@ -922,13 +922,13 @@
         <v>1.6237</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2577</v>
+        <v>0.6851</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2072</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0505</v>
+        <v>-0.0503</v>
       </c>
       <c r="V6" t="n">
         <v>-2.1444</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7623</v>
+        <v>0.3469</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7129</v>
+        <v>0.2975</v>
       </c>
       <c r="F7" t="n">
         <v>0.0494</v>
@@ -1000,10 +1000,10 @@
         <v>1.6237</v>
       </c>
       <c r="S7" t="n">
-        <v>2.8308</v>
+        <v>1.4154</v>
       </c>
       <c r="T7" t="n">
-        <v>3.2438</v>
+        <v>1.8284</v>
       </c>
       <c r="U7" t="n">
         <v>-0.4129</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0537</v>
+        <v>-0.1844</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7549</v>
+        <v>0.5504</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7010999999999999</v>
+        <v>-0.7347</v>
       </c>
       <c r="G8" t="n">
         <v>-0.731</v>
@@ -1078,13 +1078,13 @@
         <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4652</v>
+        <v>0.2271</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4288</v>
+        <v>0.2243</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0365</v>
+        <v>0.0029</v>
       </c>
       <c r="V8" t="n">
         <v>-1.0722</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. FAYE</t>
+          <t>S. HERRERA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0956</v>
+        <v>-0.2322</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.626</v>
+        <v>-2.0626</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5304</v>
+        <v>1.8303</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.651</v>
+        <v>-1.8339</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3231</v>
+        <v>-2.0144</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3279</v>
+        <v>0.1805</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2792</v>
+        <v>-1.6908</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.4265</v>
+        <v>-1.7709</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1472</v>
+        <v>0.08</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3717</v>
+        <v>-0.143</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1034</v>
+        <v>-0.2435</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4751</v>
+        <v>0.1005</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.4793</v>
+        <v>-1.3917</v>
       </c>
       <c r="R9" t="n">
-        <v>3.2473</v>
+        <v>2.3195</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9291</v>
+        <v>0.1377</v>
       </c>
       <c r="T9" t="n">
-        <v>1.1325</v>
+        <v>0.4839</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2034</v>
+        <v>-0.3462</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1418</v>
+        <v>0.5361</v>
       </c>
       <c r="W9" t="n">
+        <v>0.5361</v>
+      </c>
+      <c r="X9" t="n">
         <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-0.1418</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. HERRERA</t>
+          <t>M. FAYE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7205</v>
+        <v>-0.7189</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4164</v>
+        <v>-3.2158</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6959</v>
+        <v>2.4968</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.8339</v>
+        <v>-0.651</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.0144</v>
+        <v>-0.3231</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1805</v>
+        <v>-0.3279</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.6908</v>
+        <v>-0.2792</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.7709</v>
+        <v>-0.4265</v>
       </c>
       <c r="L10" t="n">
-        <v>0.08</v>
+        <v>0.1472</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.143</v>
+        <v>-0.3717</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2435</v>
+        <v>0.1034</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1005</v>
+        <v>-0.4751</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9278</v>
+        <v>-0.232</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.3917</v>
+        <v>-3.4793</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3195</v>
+        <v>3.2473</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3506</v>
+        <v>0.3058</v>
       </c>
       <c r="T10" t="n">
-        <v>0.13</v>
+        <v>0.5427</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4806</v>
+        <v>-0.237</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5361</v>
+        <v>-0.1418</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. DOKOSSI</t>
+          <t>J. MORGAN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2805</v>
+        <v>-1.4452</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7685</v>
+        <v>-2.0776</v>
       </c>
       <c r="F11" t="n">
-        <v>0.488</v>
+        <v>0.6324</v>
       </c>
       <c r="G11" t="n">
-        <v>1.1785</v>
+        <v>-3.8303</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2904</v>
+        <v>-0.3973</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4689</v>
+        <v>-3.433</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3075</v>
+        <v>-2.6794</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5714</v>
+        <v>0.1715</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7361</v>
+        <v>-2.8509</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.129</v>
+        <v>-1.1509</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8618</v>
+        <v>-0.5688</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7328</v>
+        <v>-0.5821</v>
       </c>
       <c r="P11" t="n">
+        <v>3.7112</v>
+      </c>
+      <c r="Q11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>-1.1598</v>
-      </c>
       <c r="R11" t="n">
-        <v>1.1598</v>
+        <v>3.7112</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7266</v>
+        <v>0.2822</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0553</v>
+        <v>0.6018</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6713</v>
+        <v>-0.3196</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.1856</v>
+        <v>-1.6083</v>
       </c>
       <c r="W11" t="n">
-        <v>-1.9716</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.214</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. MORGAN</t>
+          <t>Y. OUATTARA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.358</v>
+        <v>-1.589</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7551</v>
+        <v>-3.0326</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3971</v>
+        <v>1.4436</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.8303</v>
+        <v>-0.5844</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3973</v>
+        <v>-0.1896</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.433</v>
+        <v>-0.3948</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.6794</v>
+        <v>-0.2306</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1715</v>
+        <v>0.0539</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.8509</v>
+        <v>-0.2845</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.1509</v>
+        <v>-0.3538</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5688</v>
+        <v>-0.2435</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5821</v>
+        <v>-0.1103</v>
       </c>
       <c r="P12" t="n">
-        <v>3.7112</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q12" t="n">
+        <v>-3.9432</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.0876</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.4257</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.7158</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0.2902</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.4254</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.4254</v>
+      </c>
+      <c r="X12" t="n">
         <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>3.7112</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.3694</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0.9243</v>
-      </c>
-      <c r="U12" t="n">
-        <v>-0.5548</v>
-      </c>
-      <c r="V12" t="n">
-        <v>-1.6083</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>-1.6083</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Y. OUATTARA</t>
+          <t>A. DOKOSSI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.1109</v>
+        <v>-1.8046</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.3864</v>
+        <v>-2.091</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2756</v>
+        <v>0.2864</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.5844</v>
+        <v>1.1785</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1896</v>
+        <v>-0.2904</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3948</v>
+        <v>1.4689</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.2306</v>
+        <v>1.3075</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0539</v>
+        <v>0.5714</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.2845</v>
+        <v>0.7361</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.3538</v>
+        <v>-0.129</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2435</v>
+        <v>-0.8618</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1103</v>
+        <v>0.7328</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.8556</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.9432</v>
+        <v>-1.1598</v>
       </c>
       <c r="R13" t="n">
-        <v>2.0876</v>
+        <v>1.1598</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.09619999999999999</v>
+        <v>0.2025</v>
       </c>
       <c r="T13" t="n">
-        <v>0.362</v>
+        <v>-0.2671</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4582</v>
+        <v>0.4696</v>
       </c>
       <c r="V13" t="n">
-        <v>0.4254</v>
+        <v>-3.1856</v>
       </c>
       <c r="W13" t="n">
-        <v>0.4254</v>
+        <v>-1.9716</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="14">
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>12.4014</v>
+        <v>13.1482</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.564399999999999</v>
+        <v>-0.8177000000000008</v>
       </c>
       <c r="F14" t="n">
-        <v>13.9659</v>
+        <v>13.966</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.5025999999999988</v>
+        <v>-0.5025999999999997</v>
       </c>
       <c r="H14" t="n">
         <v>-2.3589</v>
@@ -1519,13 +1519,13 @@
         <v>1.8565</v>
       </c>
       <c r="J14" t="n">
-        <v>7.807700000000001</v>
+        <v>7.807700000000002</v>
       </c>
       <c r="K14" t="n">
-        <v>2.4889</v>
+        <v>2.488900000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>5.318499999999998</v>
+        <v>5.3185</v>
       </c>
       <c r="M14" t="n">
         <v>-8.31</v>
@@ -1534,7 +1534,7 @@
         <v>-4.848</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.4619</v>
+        <v>-3.461899999999999</v>
       </c>
       <c r="P14" t="n">
         <v>12.7573</v>
@@ -1546,16 +1546,16 @@
         <v>30.1537</v>
       </c>
       <c r="S14" t="n">
-        <v>4.089700000000001</v>
+        <v>4.8366</v>
       </c>
       <c r="T14" t="n">
-        <v>5.644899999999999</v>
+        <v>6.3917</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.555</v>
+        <v>-1.5551</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.943099999999999</v>
+        <v>-3.9431</v>
       </c>
       <c r="W14" t="n">
         <v>2.3794</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.7734</v>
+        <v>4.958</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5669</v>
+        <v>2.9207</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2065</v>
+        <v>2.0372</v>
       </c>
       <c r="G15" t="n">
         <v>3.2657</v>
@@ -1624,13 +1624,13 @@
         <v>2.5515</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.9768</v>
+        <v>-0.7923</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4402</v>
+        <v>-0.0863</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.5367</v>
+        <v>-0.7059</v>
       </c>
       <c r="V15" t="n">
         <v>1.3247</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. TAYLOR</t>
+          <t>L. VILDOZA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4088</v>
+        <v>2.058</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4266</v>
+        <v>0.4525</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0178</v>
+        <v>1.6055</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5516</v>
+        <v>1.505</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0612</v>
+        <v>0.9026999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6128</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4266</v>
+        <v>1.9659</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2857</v>
+        <v>1.1462</v>
       </c>
       <c r="L16" t="n">
-        <v>1.141</v>
+        <v>0.8196</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1249</v>
+        <v>-0.4608</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3469</v>
+        <v>-0.2435</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4718</v>
+        <v>-0.2173</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4639</v>
+        <v>2.0876</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6067</v>
+        <v>-0.0011</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>-0.1217</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6067</v>
+        <v>0.1206</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. VILDOZA</t>
+          <t>B. TAYLOR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9349</v>
+        <v>1.5604</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2166</v>
+        <v>1.5446</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7184</v>
+        <v>0.0158</v>
       </c>
       <c r="G17" t="n">
-        <v>1.505</v>
+        <v>1.5516</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9026999999999999</v>
+        <v>-0.0612</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6022999999999999</v>
+        <v>1.6128</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9659</v>
+        <v>1.4266</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1462</v>
+        <v>0.2857</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8196</v>
+        <v>1.141</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4608</v>
+        <v>0.1249</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2435</v>
+        <v>-0.3469</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2173</v>
+        <v>0.4718</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0876</v>
+        <v>0.4639</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1242</v>
+        <v>-0.4551</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3576</v>
+        <v>0.118</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7665999999999999</v>
+        <v>-0.5731000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5982</v>
+        <v>0.9749</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2492</v>
+        <v>0.6031</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3489</v>
+        <v>0.3718</v>
       </c>
       <c r="G18" t="n">
         <v>3.031</v>
@@ -1858,13 +1858,13 @@
         <v>1.8556</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5772</v>
+        <v>-0.2005</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1924</v>
+        <v>0.1614</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3848</v>
+        <v>-0.362</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2645</v>
+        <v>-0.4755</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8841</v>
+        <v>-1.5918</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1485</v>
+        <v>1.1163</v>
       </c>
       <c r="G19" t="n">
         <v>1.8594</v>
@@ -1936,13 +1936,13 @@
         <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>1.936</v>
+        <v>1.196</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2977</v>
+        <v>0.59</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6383</v>
+        <v>0.606</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2836</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5342</v>
+        <v>-0.6407</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1155</v>
+        <v>-0.7101</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6497000000000001</v>
+        <v>0.0694</v>
       </c>
       <c r="G20" t="n">
         <v>-0.6409</v>
@@ -2014,13 +2014,13 @@
         <v>2.3195</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0887</v>
+        <v>-0.0178</v>
       </c>
       <c r="T20" t="n">
-        <v>1.2151</v>
+        <v>0.3894</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.1264</v>
+        <v>-0.4072</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6778999999999999</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0262</v>
+        <v>-1.3236</v>
       </c>
       <c r="E21" t="n">
-        <v>0.09619999999999999</v>
+        <v>-0.2577</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1224</v>
+        <v>-1.066</v>
       </c>
       <c r="G21" t="n">
         <v>0.2784</v>
@@ -2092,13 +2092,13 @@
         <v>1.1598</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9274</v>
+        <v>0.63</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6686</v>
+        <v>0.3148</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2588</v>
+        <v>0.3152</v>
       </c>
       <c r="V21" t="n">
         <v>-1.0722</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4444</v>
+        <v>-1.3442</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.716</v>
+        <v>-3.4801</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2716</v>
+        <v>2.136</v>
       </c>
       <c r="G22" t="n">
         <v>-1.8923</v>
@@ -2170,13 +2170,13 @@
         <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6294999999999999</v>
+        <v>0.4707</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2671</v>
+        <v>-0.0312</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3624</v>
+        <v>0.5019</v>
       </c>
       <c r="V22" t="n">
         <v>2.3969</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.747</v>
+        <v>-2.9721</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2969</v>
+        <v>-3.061</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4502</v>
+        <v>0.0888</v>
       </c>
       <c r="G23" t="n">
         <v>-2.0622</v>
@@ -2248,13 +2248,13 @@
         <v>2.0876</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3627</v>
+        <v>-0.5878</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2082</v>
+        <v>0.0277</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.1545</v>
+        <v>-0.6155</v>
       </c>
       <c r="V23" t="n">
         <v>0.1418</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.0328</v>
+        <v>-4.348</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.7392</v>
+        <v>-4.5033</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2937</v>
+        <v>0.1553</v>
       </c>
       <c r="G24" t="n">
         <v>-4.6379</v>
@@ -2326,13 +2326,13 @@
         <v>0.9278</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1502</v>
+        <v>0.5346</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0351</v>
+        <v>0.2008</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1151</v>
+        <v>0.3339</v>
       </c>
       <c r="V24" t="n">
         <v>2.5387</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.5966</v>
+        <v>-6.1305</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.4648</v>
+        <v>-5.3469</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.1317</v>
+        <v>-0.7836</v>
       </c>
       <c r="G25" t="n">
         <v>-1.7553</v>
@@ -2404,13 +2404,13 @@
         <v>1.1598</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6146</v>
+        <v>-0.1485</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1256</v>
+        <v>-0.0077</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4889</v>
+        <v>-0.1408</v>
       </c>
       <c r="V25" t="n">
         <v>-0.2836</v>
@@ -2437,22 +2437,22 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-12.4014</v>
+        <v>-7.683300000000001</v>
       </c>
       <c r="E26" t="n">
         <v>-13.43</v>
       </c>
       <c r="F26" t="n">
-        <v>1.0284</v>
+        <v>5.746499999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>0.5024999999999986</v>
+        <v>0.5025000000000004</v>
       </c>
       <c r="H26" t="n">
         <v>2.359</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.856400000000001</v>
+        <v>-1.8564</v>
       </c>
       <c r="J26" t="n">
         <v>8.3101</v>
@@ -2482,13 +2482,13 @@
         <v>17.3965</v>
       </c>
       <c r="S26" t="n">
-        <v>-4.0898</v>
+        <v>0.6282000000000003</v>
       </c>
       <c r="T26" t="n">
-        <v>1.555200000000001</v>
+        <v>1.5552</v>
       </c>
       <c r="U26" t="n">
-        <v>-5.645</v>
+        <v>-0.9269000000000002</v>
       </c>
       <c r="V26" t="n">
         <v>3.943</v>
